--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486833_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486833_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.1598</v>
+        <v>5.0814</v>
       </c>
       <c r="E2" t="n">
-        <v>5.023</v>
+        <v>4.0439</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1368</v>
+        <v>1.0375</v>
       </c>
       <c r="G2" t="n">
         <v>1.5675</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>2.7195</v>
+        <v>1.6411</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9854</v>
+        <v>1.0063</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7341</v>
+        <v>0.6348</v>
       </c>
       <c r="V2" t="n">
         <v>0.3282</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. ESTEBANEZ ESCUDERO</t>
+          <t>I. MARTINEZ PARDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.7735</v>
+        <v>3.2451</v>
       </c>
       <c r="E3" t="n">
-        <v>4.5751</v>
+        <v>1.9431</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.8016</v>
+        <v>1.302</v>
       </c>
       <c r="G3" t="n">
-        <v>4.0634</v>
+        <v>2.1527</v>
       </c>
       <c r="H3" t="n">
-        <v>3.5794</v>
+        <v>2.6342</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4839</v>
+        <v>-0.4815</v>
       </c>
       <c r="J3" t="n">
-        <v>6.3962</v>
+        <v>2.5063</v>
       </c>
       <c r="K3" t="n">
-        <v>3.6492</v>
+        <v>2.4971</v>
       </c>
       <c r="L3" t="n">
-        <v>2.747</v>
+        <v>0.0092</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3328</v>
+        <v>-0.3536</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.0698</v>
+        <v>0.1371</v>
       </c>
       <c r="O3" t="n">
-        <v>-2.263</v>
+        <v>-0.4907</v>
       </c>
       <c r="P3" t="n">
-        <v>-1.5446</v>
+        <v>0.7723</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3515</v>
+        <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>2.3392</v>
+        <v>0.6483</v>
       </c>
       <c r="T3" t="n">
-        <v>1.075</v>
+        <v>0.7304</v>
       </c>
       <c r="U3" t="n">
-        <v>1.2642</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="V3" t="n">
-        <v>-2.0845</v>
+        <v>-0.3282</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>-0.3282</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.0845</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PARDO</t>
+          <t>M. ESTEBANEZ ESCUDERO</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4148</v>
+        <v>1.8204</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2122</v>
+        <v>4.1683</v>
       </c>
       <c r="F4" t="n">
-        <v>1.2027</v>
+        <v>-2.3479</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1527</v>
+        <v>4.0634</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6342</v>
+        <v>3.5794</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4815</v>
+        <v>0.4839</v>
       </c>
       <c r="J4" t="n">
-        <v>2.5063</v>
+        <v>6.3962</v>
       </c>
       <c r="K4" t="n">
-        <v>2.4971</v>
+        <v>3.6492</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0092</v>
+        <v>2.747</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.3536</v>
+        <v>-2.3328</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1371</v>
+        <v>-0.0698</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.4907</v>
+        <v>-2.263</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7723</v>
+        <v>-1.5446</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7377</v>
+        <v>1.3515</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.1819</v>
+        <v>1.3862</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.0005</v>
+        <v>0.6683</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1814</v>
+        <v>0.7179</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.3282</v>
+        <v>-2.0845</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.3282</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-2.0845</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. PEREZ FERNANDEZ</t>
+          <t>S. HERTEL HERMOSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5764</v>
+        <v>1.2999</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.2283</v>
+        <v>1.8455</v>
       </c>
       <c r="F5" t="n">
-        <v>0.8047</v>
+        <v>-0.5456</v>
       </c>
       <c r="G5" t="n">
-        <v>1.6369</v>
+        <v>2.2169</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.0066</v>
+        <v>2.4136</v>
       </c>
       <c r="I5" t="n">
-        <v>1.6435</v>
+        <v>-0.1967</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2172</v>
+        <v>2.7353</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.351</v>
+        <v>2.69</v>
       </c>
       <c r="L5" t="n">
-        <v>2.5682</v>
+        <v>0.0453</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5803</v>
+        <v>-0.5184</v>
       </c>
       <c r="N5" t="n">
-        <v>0.3443</v>
+        <v>-0.2764</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9247</v>
+        <v>-0.242</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.9308</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9654</v>
+        <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5847</v>
+        <v>-0.3377</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1651</v>
+        <v>0.0757</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4196</v>
+        <v>-0.4134</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>S. HERTEL HERMOSA</t>
+          <t>P. PEREZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4351</v>
+        <v>0.7364000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>1.3284</v>
+        <v>-0.1179</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.8933</v>
+        <v>0.8542999999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>2.2169</v>
+        <v>1.6369</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4136</v>
+        <v>-0.0066</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1967</v>
+        <v>1.6435</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7353</v>
+        <v>2.2172</v>
       </c>
       <c r="K6" t="n">
-        <v>2.69</v>
+        <v>-0.351</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0453</v>
+        <v>2.5682</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.5184</v>
+        <v>-0.5803</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2764</v>
+        <v>0.3443</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.242</v>
+        <v>-0.9247</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.5792</v>
+        <v>-1.9308</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>0.9654</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.2025</v>
+        <v>0.7447</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4415</v>
+        <v>0.2754</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.761</v>
+        <v>0.4693</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2866</v>
+        <v>0.3652</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8</v>
+        <v>0.9035</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5135</v>
+        <v>-0.5383</v>
       </c>
       <c r="G7" t="n">
         <v>-0.4967</v>
@@ -1000,13 +1000,13 @@
         <v>0.5792</v>
       </c>
       <c r="S7" t="n">
-        <v>0.2041</v>
+        <v>0.2826</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4963</v>
+        <v>0.5997</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2922</v>
+        <v>-0.3171</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1661</v>
+        <v>0.0048</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.248</v>
+        <v>0.2209</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0819</v>
+        <v>-0.2161</v>
       </c>
       <c r="G8" t="n">
         <v>-1.3305</v>
@@ -1078,13 +1078,13 @@
         <v>0.5792</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0053</v>
+        <v>0.1655</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3581</v>
+        <v>0.827</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3635</v>
+        <v>-0.6615</v>
       </c>
       <c r="V8" t="n">
         <v>1.5559</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4674</v>
+        <v>-0.4963</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.9029</v>
+        <v>-1.0063</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4355</v>
+        <v>0.51</v>
       </c>
       <c r="G9" t="n">
         <v>-0.7199</v>
@@ -1156,13 +1156,13 @@
         <v>0.3862</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5461</v>
+        <v>0.5171</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4411</v>
+        <v>0.3377</v>
       </c>
       <c r="U9" t="n">
-        <v>0.105</v>
+        <v>0.1795</v>
       </c>
       <c r="V9" t="n">
         <v>0.2856</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>C. LUENGO NEVADO</t>
+          <t>L. BAQUEICOA PADRON</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.9282</v>
+        <v>-1.2691</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0547</v>
+        <v>-0.0138</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9829</v>
+        <v>-1.2553</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.4482</v>
+        <v>0.1103</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3102</v>
+        <v>-0.0276</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.138</v>
+        <v>0.1379</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0497</v>
+        <v>0.0414</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.7234</v>
+        <v>0.0414</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7732</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4979</v>
+        <v>0.0689</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4132</v>
+        <v>-0.06900000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9111</v>
+        <v>0.1379</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.3862</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5792</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5626</v>
+        <v>-0.1517</v>
       </c>
       <c r="T10" t="n">
-        <v>1.6269</v>
+        <v>-0.0552</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.0642</v>
+        <v>-0.0965</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.6565</v>
+        <v>-1.2277</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.6565</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>L. BAQUEICOA PADRON</t>
+          <t>C. LUENGO NEVADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.294</v>
+        <v>-1.7597</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0138</v>
+        <v>-0.8761</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.2802</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>0.1103</v>
+        <v>-0.4482</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0276</v>
+        <v>-0.3102</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1379</v>
+        <v>-0.138</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0414</v>
+        <v>0.0497</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0414</v>
+        <v>-0.7234</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>0.7732</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0689</v>
+        <v>-0.4979</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.06900000000000001</v>
+        <v>0.4132</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1379</v>
+        <v>-0.9111</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1765</v>
+        <v>-0.2688</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0552</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1213</v>
+        <v>-0.9649</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2277</v>
+        <v>-0.6565</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.3756</v>
+        <v>-1.9122</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.6428</v>
+        <v>-1.2291</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.7328</v>
+        <v>-0.6832</v>
       </c>
       <c r="G12" t="n">
         <v>-1.181</v>
@@ -1390,13 +1390,13 @@
         <v>0.1931</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.16</v>
+        <v>0.3034</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2484</v>
+        <v>0.1653</v>
       </c>
       <c r="U12" t="n">
-        <v>0.08840000000000001</v>
+        <v>0.1381</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2277</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.0634</v>
+        <v>-8.2125</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.1389</v>
+        <v>-5.5114</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.9246</v>
+        <v>-2.7011</v>
       </c>
       <c r="G13" t="n">
         <v>-4.7095</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2647</v>
+        <v>0.5863</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.166</v>
+        <v>0.4615</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0987</v>
+        <v>0.1248</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6138</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.648500000000002</v>
+        <v>-1.096600000000002</v>
       </c>
       <c r="E14" t="n">
-        <v>3.818700000000002</v>
+        <v>4.3706</v>
       </c>
       <c r="F14" t="n">
         <v>-5.4673</v>
       </c>
       <c r="G14" t="n">
-        <v>2.861900000000001</v>
+        <v>2.861899999999999</v>
       </c>
       <c r="H14" t="n">
         <v>7.5867</v>
@@ -1528,7 +1528,7 @@
         <v>5.110199999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-9.495799999999999</v>
+        <v>-9.495800000000001</v>
       </c>
       <c r="N14" t="n">
         <v>0.3388</v>
@@ -1546,13 +1546,13 @@
         <v>9.653799999999999</v>
       </c>
       <c r="S14" t="n">
-        <v>4.965299999999999</v>
+        <v>5.517000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>5.236299999999999</v>
+        <v>5.7882</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.271</v>
+        <v>-0.2711</v>
       </c>
       <c r="V14" t="n">
         <v>-3.6831</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.9774</v>
+        <v>7.42</v>
       </c>
       <c r="E15" t="n">
-        <v>4.3035</v>
+        <v>4.4069</v>
       </c>
       <c r="F15" t="n">
-        <v>2.674</v>
+        <v>3.0132</v>
       </c>
       <c r="G15" t="n">
         <v>5.8133</v>
@@ -1624,13 +1624,13 @@
         <v>1.5446</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3805</v>
+        <v>0.0621</v>
       </c>
       <c r="T15" t="n">
-        <v>0.2204</v>
+        <v>0.3238</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.6009</v>
+        <v>-0.2617</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.6309</v>
+        <v>3.6987</v>
       </c>
       <c r="E16" t="n">
-        <v>2.5367</v>
+        <v>1.5024</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0943</v>
+        <v>2.1962</v>
       </c>
       <c r="G16" t="n">
         <v>1.6809</v>
@@ -1702,13 +1702,13 @@
         <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>1.6218</v>
+        <v>0.6896</v>
       </c>
       <c r="T16" t="n">
-        <v>1.6269</v>
+        <v>0.5926</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.005</v>
+        <v>0.0969</v>
       </c>
       <c r="V16" t="n">
         <v>0.9421</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.5573</v>
+        <v>2.7986</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5746</v>
+        <v>2.678</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0173</v>
+        <v>0.1206</v>
       </c>
       <c r="G17" t="n">
         <v>3.2609</v>
@@ -1780,13 +1780,13 @@
         <v>0.3862</v>
       </c>
       <c r="S17" t="n">
-        <v>0.331</v>
+        <v>0.5723</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0004</v>
+        <v>0.1031</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3313</v>
+        <v>0.4692</v>
       </c>
       <c r="V17" t="n">
         <v>-1.2277</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. IYOHA OSARENKHOE</t>
+          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4344</v>
+        <v>1.7431</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.1292</v>
+        <v>3.7404</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5635</v>
+        <v>-1.9973</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.7071</v>
+        <v>0.4905</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.0687</v>
+        <v>-0.5178</v>
       </c>
       <c r="I18" t="n">
-        <v>0.3617</v>
+        <v>1.0083</v>
       </c>
       <c r="J18" t="n">
-        <v>-1.7615</v>
+        <v>3.6782</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.965</v>
+        <v>1.7588</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2035</v>
+        <v>1.9194</v>
       </c>
       <c r="M18" t="n">
-        <v>1.0544</v>
+        <v>-3.1878</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8962</v>
+        <v>-2.2766</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1582</v>
+        <v>-0.9111</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7723</v>
+        <v>0.1931</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.9308</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6548</v>
+        <v>-1.1102</v>
       </c>
       <c r="T18" t="n">
-        <v>2.2888</v>
+        <v>-0.4624</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.6341</v>
+        <v>-0.6478</v>
       </c>
       <c r="V18" t="n">
+        <v>2.1698</v>
+      </c>
+      <c r="W18" t="n">
+        <v>2.4554</v>
+      </c>
+      <c r="X18" t="n">
         <v>-0.2856</v>
-      </c>
-      <c r="W18" t="n">
-        <v>-0.6565</v>
-      </c>
-      <c r="X18" t="n">
-        <v>0.3709</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1627</v>
+        <v>1.622</v>
       </c>
       <c r="E19" t="n">
-        <v>3.32</v>
+        <v>3.2166</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.1573</v>
+        <v>-1.5946</v>
       </c>
       <c r="G19" t="n">
         <v>2.9364</v>
@@ -1936,13 +1936,13 @@
         <v>2.1239</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.4454</v>
+        <v>-0.9862</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4143</v>
+        <v>-0.5177</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0311</v>
+        <v>-0.4685</v>
       </c>
       <c r="V19" t="n">
         <v>-0.3282</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>G. GARRIDO GUERREIRO DE SOUSA</t>
+          <t>A. DELICADO DOMINGUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.0826</v>
+        <v>1.1054</v>
       </c>
       <c r="E20" t="n">
-        <v>3.4302</v>
+        <v>1.4476</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.3476</v>
+        <v>-0.3422</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4905</v>
+        <v>1.3151</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5178</v>
+        <v>0.1169</v>
       </c>
       <c r="I20" t="n">
-        <v>1.0083</v>
+        <v>1.1982</v>
       </c>
       <c r="J20" t="n">
-        <v>3.6782</v>
+        <v>3.9445</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7588</v>
+        <v>1.2903</v>
       </c>
       <c r="L20" t="n">
-        <v>1.9194</v>
+        <v>2.6541</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1878</v>
+        <v>-2.6294</v>
       </c>
       <c r="N20" t="n">
-        <v>-2.2766</v>
+        <v>-1.1734</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.9111</v>
+        <v>-1.456</v>
       </c>
       <c r="P20" t="n">
         <v>0.1931</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9308</v>
+        <v>-2.1239</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1239</v>
+        <v>2.3169</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7708</v>
+        <v>-0.731</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7727000000000001</v>
+        <v>-0.373</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.9981</v>
+        <v>-0.358</v>
       </c>
       <c r="V20" t="n">
-        <v>2.1698</v>
+        <v>0.3282</v>
       </c>
       <c r="W20" t="n">
-        <v>2.4554</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2856</v>
+        <v>0.3282</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. DELICADO DOMINGUEZ</t>
+          <t>D. IYOHA OSARENKHOE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.009</v>
+        <v>0.4002</v>
       </c>
       <c r="E21" t="n">
-        <v>1.2408</v>
+        <v>-1.5771</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2318</v>
+        <v>1.9772</v>
       </c>
       <c r="G21" t="n">
-        <v>1.3151</v>
+        <v>-0.7071</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1169</v>
+        <v>-1.0687</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1982</v>
+        <v>0.3617</v>
       </c>
       <c r="J21" t="n">
-        <v>3.9445</v>
+        <v>-1.7615</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2903</v>
+        <v>-1.965</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6541</v>
+        <v>0.2035</v>
       </c>
       <c r="M21" t="n">
-        <v>-2.6294</v>
+        <v>1.0544</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1734</v>
+        <v>0.8962</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.456</v>
+        <v>0.1582</v>
       </c>
       <c r="P21" t="n">
-        <v>0.1931</v>
+        <v>0.7723</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1239</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.3169</v>
+        <v>0.7723</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8274</v>
+        <v>0.6205000000000001</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5798</v>
+        <v>0.8409</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2475</v>
+        <v>-0.2204</v>
       </c>
       <c r="V21" t="n">
-        <v>0.3282</v>
+        <v>-0.2856</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6565</v>
       </c>
       <c r="X21" t="n">
-        <v>0.3282</v>
+        <v>0.3709</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.3889</v>
+        <v>-0.1531</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4699</v>
+        <v>-0.1597</v>
       </c>
       <c r="F22" t="n">
-        <v>0.08110000000000001</v>
+        <v>0.0066</v>
       </c>
       <c r="G22" t="n">
         <v>-0.1186</v>
@@ -2170,13 +2170,13 @@
         <v>0.1931</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.2703</v>
+        <v>-0.0345</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5518</v>
+        <v>-0.2416</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2815</v>
+        <v>0.2071</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.8094</v>
+        <v>-0.6703</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.8558</v>
+        <v>-2.0284</v>
       </c>
       <c r="F23" t="n">
-        <v>1.0464</v>
+        <v>1.3581</v>
       </c>
       <c r="G23" t="n">
         <v>-1.8977</v>
@@ -2248,13 +2248,13 @@
         <v>0.7723</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6841</v>
+        <v>0.455</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3864</v>
+        <v>0.441</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.2977</v>
+        <v>0.014</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.639</v>
+        <v>-3.7687</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.8088</v>
+        <v>-1.0157</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.8302</v>
+        <v>-2.753</v>
       </c>
       <c r="G24" t="n">
         <v>-5.9497</v>
@@ -2326,13 +2326,13 @@
         <v>1.7377</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5461</v>
+        <v>-0.6758</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.0557</v>
+        <v>-0.2625</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4905</v>
+        <v>-0.4133</v>
       </c>
       <c r="V24" t="n">
         <v>2.0845</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.4106</v>
+        <v>-4.5569</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.9975</v>
+        <v>-4.4804</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.413</v>
+        <v>-0.0765</v>
       </c>
       <c r="G25" t="n">
         <v>-4.8079</v>
@@ -2404,13 +2404,13 @@
         <v>1.1585</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0813</v>
+        <v>-0.2277</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.3864</v>
+        <v>0.1307</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6949</v>
+        <v>-0.3584</v>
       </c>
       <c r="V25" t="n">
         <v>0.2856</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-5.958</v>
+        <v>-5.2326</v>
       </c>
       <c r="E26" t="n">
-        <v>-2.6772</v>
+        <v>-2.2635</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.2808</v>
+        <v>-2.9691</v>
       </c>
       <c r="G26" t="n">
         <v>-4.8778</v>
@@ -2482,13 +2482,13 @@
         <v>0.7723</v>
       </c>
       <c r="S26" t="n">
-        <v>-1.5669</v>
+        <v>-0.8415</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.7175</v>
+        <v>-0.3038</v>
       </c>
       <c r="U26" t="n">
-        <v>-0.8494</v>
+        <v>-0.5377</v>
       </c>
       <c r="V26" t="n">
         <v>-0.2856</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>1.6484</v>
+        <v>4.406400000000003</v>
       </c>
       <c r="E27" t="n">
-        <v>5.4674</v>
+        <v>5.4671</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.8187</v>
+        <v>-1.060799999999999</v>
       </c>
       <c r="G27" t="n">
         <v>-2.8617</v>
@@ -2545,7 +2545,7 @@
         <v>-12.3577</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.2477</v>
+        <v>-7.247700000000001</v>
       </c>
       <c r="O27" t="n">
         <v>-5.109999999999999</v>
@@ -2560,13 +2560,13 @@
         <v>15.4463</v>
       </c>
       <c r="S27" t="n">
-        <v>-4.965199999999999</v>
+        <v>-2.2074</v>
       </c>
       <c r="T27" t="n">
-        <v>0.2710999999999997</v>
+        <v>0.2710999999999998</v>
       </c>
       <c r="U27" t="n">
-        <v>-5.2364</v>
+        <v>-2.4786</v>
       </c>
       <c r="V27" t="n">
         <v>3.6831</v>
